--- a/mario/tools/cvxlab/AuSteel/model_settings.xlsx
+++ b/mario/tools/cvxlab/AuSteel/model_settings.xlsx
@@ -8,10 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4cb83e15a8550b8f/Documenti/GitHub/MARIO/mario/tools/cvxlab/AuSteel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{09ACD022-6DB1-493C-9797-2C4B7F7B13D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A38844-5836-406F-BB16-E4547469D8C0}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{09ACD022-6DB1-493C-9797-2C4B7F7B13D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80CFF4D1-DFE0-4812-8505-E19106F7982A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5885115D-3BA4-42C5-A7B9-D2CCF4E386B9}"/>
-    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{ADE65AC1-7326-4C1C-AEEF-E9867C94CCED}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{5885115D-3BA4-42C5-A7B9-D2CCF4E386B9}"/>
   </bookViews>
   <sheets>
     <sheet name="problem" sheetId="5" r:id="rId1"/>
@@ -19,7 +18,7 @@
     <sheet name="structure_sets" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">structure_variables!$A$1:$P$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">structure_variables!$A$1:$P$14</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="80">
   <si>
     <t>problem_key</t>
   </si>
@@ -56,9 +55,6 @@
     <t>description</t>
   </si>
   <si>
-    <t>Q - uu @ X - Y @ I_col == 0</t>
-  </si>
-  <si>
     <t>Link Q, Y, X</t>
   </si>
   <si>
@@ -251,21 +247,6 @@
     <t>E</t>
   </si>
   <si>
-    <t>I_col</t>
-  </si>
-  <si>
-    <t>Auxiliary column vector</t>
-  </si>
-  <si>
-    <t>constant</t>
-  </si>
-  <si>
-    <t>region_to, cons_categ</t>
-  </si>
-  <si>
-    <t>sum_vector</t>
-  </si>
-  <si>
     <t>set_key</t>
   </si>
   <si>
@@ -297,6 +278,9 @@
   </si>
   <si>
     <t>Satellite accounts (rows of E)</t>
+  </si>
+  <si>
+    <t>Q - uu @ X - Y == 0</t>
   </si>
 </sst>
 </file>
@@ -753,55 +737,55 @@
     </row>
     <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C8" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="5"/>
     </row>
@@ -816,7 +800,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99EF8F26-7547-4076-9880-E796E9F04B5A}">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
@@ -835,465 +819,425 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>42</v>
-      </c>
       <c r="F3" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>45</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>48</v>
-      </c>
       <c r="F5" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R5" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>50</v>
-      </c>
       <c r="C6" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="C7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>53</v>
-      </c>
       <c r="F7" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P7" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>56</v>
-      </c>
       <c r="E8" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="C9" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="F9" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="K9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>62</v>
-      </c>
       <c r="F10" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K10"/>
       <c r="L10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>64</v>
-      </c>
       <c r="C11" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J11" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" t="s">
-        <v>39</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K11"/>
       <c r="L11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M11"/>
       <c r="N11"/>
       <c r="O11"/>
-      <c r="P11" t="s">
-        <v>39</v>
-      </c>
+      <c r="P11"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
         <v>65</v>
       </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
       <c r="C12" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
       <c r="O12" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>67</v>
-      </c>
       <c r="J13" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
       <c r="O13" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14"/>
       <c r="E14" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G14"/>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
       <c r="O14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P14" s="10"/>
       <c r="R14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15"/>
-      <c r="E15" t="s">
-        <v>72</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-      <c r="K15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L15"/>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
-      <c r="P15" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q15"/>
-      <c r="R15"/>
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P15" xr:uid="{99EF8F26-7547-4076-9880-E796E9F04B5A}"/>
+  <autoFilter ref="A1:P14" xr:uid="{99EF8F26-7547-4076-9880-E796E9F04B5A}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1311,91 +1255,91 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1404,26 +1348,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="90e7079a-7589-470d-892b-836f3f5ab9a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9ef6bf99-292f-445d-95df-6a8984d5eb85" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101007BAED4C651AD5C4F9C61E3D439BD1465" ma:contentTypeVersion="11" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="3916dc5588df290b35e5c499b507bc33">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="90e7079a-7589-470d-892b-836f3f5ab9a4" xmlns:ns3="9ef6bf99-292f-445d-95df-6a8984d5eb85" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e3fae628afbc47c424dc6703fd07071" ns2:_="" ns3:_="">
     <xsd:import namespace="90e7079a-7589-470d-892b-836f3f5ab9a4"/>
@@ -1618,10 +1542,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="90e7079a-7589-470d-892b-836f3f5ab9a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9ef6bf99-292f-445d-95df-6a8984d5eb85" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91788BB2-4A3F-4B3D-BB9A-4A497CBAE5D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44CBF23E-31B0-4D8A-8D2D-FCBF8308E3B6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="90e7079a-7589-470d-892b-836f3f5ab9a4"/>
+    <ds:schemaRef ds:uri="9ef6bf99-292f-445d-95df-6a8984d5eb85"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1638,20 +1593,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44CBF23E-31B0-4D8A-8D2D-FCBF8308E3B6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91788BB2-4A3F-4B3D-BB9A-4A497CBAE5D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="90e7079a-7589-470d-892b-836f3f5ab9a4"/>
-    <ds:schemaRef ds:uri="9ef6bf99-292f-445d-95df-6a8984d5eb85"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>